--- a/data/case-study-manufacturing-quality--manufacturing_quality.xlsx
+++ b/data/case-study-manufacturing-quality--manufacturing_quality.xlsx
@@ -9911,7 +9911,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WHAT IS CAPTURED: a quality-control sample across three lines and two shifts.</t>
+          <t>WHAT IS CAPTURED: a quality-control sample across three lines and two shifts (a realistic teaching dataset written for the book).</t>
         </is>
       </c>
     </row>
